--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -447,7 +447,6 @@
           <t>2026-09-13T17:30:13.610781+00:00</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
@@ -460,7 +459,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Content quality review failed: Incorrect count of four‑digit strings (should be 10000, not 9000).; Wrong worst‑case iteration claim for 1098 (it reaches 6174 in 3 steps, not 7).</t>
         </is>
       </c>
     </row>

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -479,7 +479,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Error code: 413 - {'error': {'message': 'Request too large for model `openai/gpt-oss-120b` in organization `org_01kzfy82cxeyvbp25hn08bgge3` service tier `on_demand` on tokens per minute (TPM): Limit 8000, Requested 9270, please reduce your message size and try again. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
         </is>
       </c>
     </row>

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -499,9 +499,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/animate_the_triangle_angle_sum_theorem_and_visually_prove_wh/final_video.mp4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/animate_the_triangle_angle_sum_theorem_and_visually_prove_wh/thumbnail.png</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gh21lVnAG2g</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Gh21lVnAG2g</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-13T18:25:45.481701+00:00</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -527,7 +527,6 @@
           <t>2026-09-13T18:25:45.481701+00:00</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -970,7 +969,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>SKIPPED_DUPLICATE</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Duplicate topic: Kaprekar constant 6174 is already uploaded as prompt 31.</t>
         </is>
       </c>
     </row>

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -539,7 +539,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Content quality review failed: Incorrect claim that the Kaprekar constant appears in "base‑110"; the discussion should be limited to base‑10 only.</t>
         </is>
       </c>
     </row>

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -559,7 +559,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Content quality review failed: The script claims that "the pair (7641,1467) is the only ordered pair of four‑digit numbers whose difference is exactly the constant." This statement is not part of the supported claims for the four‑digit Kaprekar routine and is not generally true without additional qualifiers (e.g., that the numbers are the descending and ascending arrangements of the same digits). It introduces an unsupported factual claim.</t>
         </is>
       </c>
     </row>

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -579,7 +579,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Error code: 429 - {'error': {'message': 'Rate limit reached for model `openai/gpt-oss-120b` in organization `org_01kzfy82cxeyvbp25hn08bgge3` service tier `on_demand` on tokens per minute (TPM): Limit 8000, Used 3847, Requested 4550. Please try again in 2.9775s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
         </is>
       </c>
     </row>

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -599,7 +599,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Content quality review failed: Incorrect characterization of 6174 as a "2‑cycle"; it is a fixed point of the Kaprekar transformation.</t>
         </is>
       </c>
     </row>

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -459,12 +459,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Content quality review failed: Incorrect count of four‑digit strings (should be 10000, not 9000).; Wrong worst‑case iteration claim for 1098 (it reaches 6174 in 3 steps, not 7).</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -479,12 +474,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Error code: 413 - {'error': {'message': 'Request too large for model `openai/gpt-oss-120b` in organization `org_01kzfy82cxeyvbp25hn08bgge3` service tier `on_demand` on tokens per minute (TPM): Limit 8000, Requested 9270, please reduce your message size and try again. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -539,14 +529,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Content quality review failed: Incorrect claim that the Kaprekar constant appears in "base‑110"; the discussion should be limited to base‑10 only.</t>
-        </is>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -459,7 +459,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Error code: 429 - {'error': {'message': 'Rate limit reached for model `openai/gpt-oss-120b` in organization `org_01kzfy82cxeyvbp25hn08bgge3` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199849, Requested 3462. Please try again in 23m50.352s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
         </is>
       </c>
     </row>
@@ -532,7 +537,6 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -479,7 +479,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Error code: 429 - {'error': {'message': 'Rate limit reached for model `openai/gpt-oss-120b` in organization `org_01kzfy82cxeyvbp25hn08bgge3` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199849, Requested 1177. Please try again in 7m23.232s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
         </is>
       </c>
     </row>

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -459,12 +459,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Error code: 429 - {'error': {'message': 'Rate limit reached for model `openai/gpt-oss-120b` in organization `org_01kzfy82cxeyvbp25hn08bgge3` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199849, Requested 3462. Please try again in 23m50.352s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -479,14 +474,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Error code: 429 - {'error': {'message': 'Rate limit reached for model `openai/gpt-oss-120b` in organization `org_01kzfy82cxeyvbp25hn08bgge3` service tier `on_demand` on tokens per day (TPD): Limit 200000, Used 199849, Requested 1177. Please try again in 7m23.232s. Need more tokens? Upgrade to Dev Tier today at https://console.groq.com/settings/billing', 'type': 'tokens', 'code': 'rate_limit_exceeded'}}</t>
-        </is>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -459,9 +459,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
+          <t>SCRIPT_GENERATED</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -477,7 +478,6 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -459,10 +459,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SCRIPT_GENERATED</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Invalid \escape: line 1 column 628 (char 627)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -479,9 +479,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/explain_fermat_s_last_theorem_what_does_a_n_b_n_c_n_claim_an/final_video.mp4</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/explain_fermat_s_last_theorem_what_does_a_n_b_n_c_n_claim_an/thumbnail.png</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>YgVF2iXlldg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://youtu.be/YgVF2iXlldg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-09-13T22:37:26.191669+00:00</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -459,14 +459,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Invalid \escape: line 1 column 628 (char 627)</t>
-        </is>
-      </c>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -507,7 +503,6 @@
           <t>2026-09-13T22:37:26.191669+00:00</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -459,10 +459,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Render failed after repair attempts: Duration 5.1s is outside 60.0-360.0s</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -559,7 +559,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Render failed after repair attempts: Generated code has invalid Python syntax: '(' was never closed (&lt;unknown&gt;, line 255)</t>
         </is>
       </c>
     </row>

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -579,7 +579,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Render failed after repair attempts: Duration 23.4s is outside 60.0-360.0s</t>
         </is>
       </c>
     </row>

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -599,7 +599,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                         │
+│ /home/runner/work/math-youtube-agent/math-youtube-agent/generated/show_the_i │
+│ ntercept_theorem_using_parallel_lines_moving_point/scene.py:68 in construct  │
+│                                                                              │
+│    65 │   │                                                                  │
+│    66 │   │   # ---------- Scene 3: Angle Equality ----------                │
+│    67 │   │   # Zoom into intersection points                                │
+│ ❱  68 │   │   zoom = ZoomInFromCenter(AC, scale_factor=2)                    │
+│    69 │   │   self.play(zoom)                                                │
+│    70 │   │   self.wait(1)                                                   │
+│    71                                                                        │
+╰──────────────────────────────────────────────────────────────────────────────╯
+NameError: name 'ZoomInFromCenter' is not defined
+</t>
         </is>
       </c>
     </row>

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -632,9 +632,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/animate_the_law_of_sines_by_dropping_an_altitude_and_derivin/final_video.mp4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/animate_the_law_of_sines_by_dropping_an_altitude_and_derivin/thumbnail.png</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>N2Eh0j40vnY</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://youtu.be/N2Eh0j40vnY</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:47:43.010370+00:00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -660,7 +660,6 @@
           <t>2026-09-14T00:47:43.010370+00:00</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -673,7 +672,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ies (c^{2}=a^{2}+b^{2}), which is the Pythagorean theorem.\\n\\nexample":"Consider a right triangle with legs (a=3) and (b=4). Using the law of cosines with (C=90^circ):\\n\\n[\\nc^{2}=3^{2}+4^{2}-2(3)(4)cos 90^circ=9+16-24(0)=25\\n]\\n\\nSo (c=sqrt{25}=5), confirming the classic 3‑4‑5 triangle.\\n\\ninteresting_fact":"The law of cosines is sometimes called the \\"cosine rule\\" and is a direct generalization of the Pythagorean theorem. It also appears in vector mathematics: the dot product of two vectors (mathbf{u}) and (mathbf{v}) is (|mathbf{u}||mathbf{v}|cos\\theta), leading to (|mathbf{u}-mathbf{v}|^{2}=|mathbf{u}|^{2}+|mathbf{v}|^{2}-2|mathbf{u}||mathbf{v}|cos\\theta), which is the law of cosines in vector form.\\n\\nconclusion":"The law of cosines unifies the geometry of all triangles, reducing neatly to the Pythagorean theorem when the angle is a right angle. Understanding this relationship deepens our appreciation of how trigonometric identities govern the shape of space."}'}}</t>
         </is>
       </c>
     </row>

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -692,9 +692,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/explain_heron_s_formula_for_triangle_area_and_animate_how_si/final_video.mp4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/explain_heron_s_formula_for_triangle_area_and_animate_how_si/thumbnail.png</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>WUQHqTCoyHI</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://youtu.be/WUQHqTCoyHI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:11:15.929051+00:00</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -720,7 +720,6 @@
           <t>2026-09-14T02:11:15.929051+00:00</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -733,7 +732,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                               │
+│ /opt/hostedtoolcache/Python/3.11.16/x64/lib/python3.11/site-packages/manim/a │
+│ nimation/animation.py:192 in _typecheck_input                                │
+│                                                                              │
+│   189 │   │   if mobject is None:                                            │
+│   190 │   │   │   logger.debug("Animation with empty mobject")               │
+│   191 │   │   elif not isinstance(mobject, (Mobject, OpenGLMobject)):        │
+│ ❱ 192 │   │   │   raise TypeError("Animation only works on Mobjects")        │
+│   193 │                                                                      │
+│   194 │   def __str__(self) -&gt; str:                                          │
+│   195 │   │   if self.name:                                                  │
+╰──────────────────────────────────────────────────────────────────────────────╯
+TypeError: Animation only works on Mobjects
+</t>
         </is>
       </c>
     </row>
@@ -748,7 +765,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Content quality review failed: Scene 4 contains a factual error: the narration claims the face count increases by 4 when, in fact, it increases by 3. This inconsistency undermines the instructional integrity of the segment.</t>
         </is>
       </c>
     </row>
@@ -763,7 +785,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Render failed after repair attempts: Generated code has invalid Python syntax: unterminated string literal (detected at line 256) (&lt;unknown&gt;, line 256)</t>
         </is>
       </c>
     </row>

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -805,9 +805,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/animate_menelaus_theorem_using_a_line_crossing_the_three_sid/final_video.mp4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/animate_menelaus_theorem_using_a_line_crossing_the_three_sid/thumbnail.png</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>nK4DV2nN8jA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://youtu.be/nK4DV2nN8jA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-14T03:32:31.566865+00:00</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -833,7 +833,6 @@
           <t>2026-09-14T03:32:31.566865+00:00</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
@@ -846,9 +845,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/explain_the_fundamental_theorem_of_arithmetic_why_every_inte/final_video.mp4</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/explain_the_fundamental_theorem_of_arithmetic_why_every_inte/thumbnail.png</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>lT9Nx-5ydi0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://youtu.be/lT9Nx-5ydi0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:48:04.956091+00:00</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -873,7 +873,6 @@
           <t>2026-09-14T04:48:04.956091+00:00</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -886,7 +885,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Render failed after repair attempts: Duration 41.0s is outside 60.0-360.0s</t>
         </is>
       </c>
     </row>
@@ -901,9 +905,35 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/explain_wilson_s_theorem_and_show_its_surprising_connection_/final_video.mp4</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/explain_wilson_s_theorem_and_show_its_surprising_connection_/thumbnail.png</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>wTAuaJ8UqFg</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://youtu.be/wTAuaJ8UqFg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-09-14T05:55:12.965491+00:00</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="11" t="inlineStr">

--- a/input/prompts.xlsx
+++ b/input/prompts.xlsx
@@ -933,7 +933,6 @@
           <t>2026-09-14T05:55:12.965491+00:00</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
@@ -946,7 +945,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Render failed after repair attempts: Duration 8.8s is outside 60.0-360.0s</t>
         </is>
       </c>
     </row>
@@ -961,9 +965,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/show_the_geometric_proof_that_1_3_5_2n_1_n_by_growing_square/final_video.mp4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/math-youtube-agent/math-youtube-agent/generated/show_the_geometric_proof_that_1_3_5_2n_1_n_by_growing_square/thumbnail.png</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>a0SyEUg3MNo</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://youtu.be/a0SyEUg3MNo</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-09-14T06:58:39.939805+00:00</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
